--- a/config/rulebook.xlsx
+++ b/config/rulebook.xlsx
@@ -1887,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2078,4286 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>asset_abs_BS000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BS000 流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>asset_abs_BS001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BS001 货币资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>asset_abs_BS002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BS002 交易性金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>asset_abs_BS003</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BS003 衍生金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>asset_abs_BS004</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BS004 应收票据及应收账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>asset_abs_BS005</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BS005 应收票据</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>asset_abs_BS006</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BS006 应收账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>asset_abs_BS007</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BS007 应收款项融资</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>asset_abs_BS008</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BS008 预付款项</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>asset_abs_BS009</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BS009 其他应收款(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>asset_abs_BS010</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BS010 应收股利</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>asset_abs_BS011</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BS011 应收利息</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>asset_abs_BS012</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BS012 其他应收款</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>asset_abs_BS013</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BS013 买入返售金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>asset_abs_BS014</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BS014 存货</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>asset_abs_BS015</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BS015 其中：消耗性生物资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>asset_abs_BS016</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BS016 合同资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>asset_abs_BS017</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BS017 划分为持有待售的资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>asset_abs_BS018</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BS018 一年内到期的非流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>asset_abs_BS019</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BS019 待摊费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>asset_abs_BS020</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BS020 其他流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>asset_abs_BS021</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BS021 其他金融类流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>asset_abs_BS022</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BS022 结算备付金</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>asset_abs_BS023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BS023 拆出资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>asset_abs_BS024</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BS024 应收保费</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>asset_abs_BS025</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BS025 应收分保账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>asset_abs_BS026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BS026 应收分保合同准备金</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>asset_abs_BS027</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BS027 流动资产合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>asset_abs_BS028</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BS028 非流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>asset_abs_BS029</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BS029 发放贷款及垫款</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>asset_abs_BS030</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BS030 以公允价值且其变动计入其他综合收益的金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>asset_abs_BS031</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BS031 以摊余成本计量的金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>asset_abs_BS032</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BS032 债权投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>asset_abs_BS033</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BS033 其他债权投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>asset_abs_BS034</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BS034 可供出售金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>asset_abs_BS035</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BS035 其他权益工具投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>asset_abs_BS036</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BS036 持有至到期投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>asset_abs_BS037</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BS037 其他非流动金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>asset_abs_BS038</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BS038 长期应收款</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>asset_abs_BS039</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BS039 长期股权投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>asset_abs_BS040</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BS040 投资性房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>asset_abs_BS041</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BS041 固定资产(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>asset_abs_BS042</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BS042 固定资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>asset_abs_BS043</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BS043 固定资产清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>asset_abs_BS044</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BS044 在建工程(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>asset_abs_BS045</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BS045 在建工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>asset_abs_BS046</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BS046 工程物资</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>asset_abs_BS047</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BS047 生产性生物资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>asset_abs_BS048</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BS048 油气资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>asset_abs_BS049</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BS049 使用权资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>asset_abs_BS050</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BS050 无形资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>asset_abs_BS051</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BS051 开发支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>asset_abs_BS052</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BS052 商誉</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>asset_abs_BS053</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BS053 长期待摊费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>asset_abs_BS054</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BS054 递延所得税资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>asset_abs_BS055</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BS055 其他非流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>asset_abs_BS056</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BS056 非流动资产合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>asset_abs_BS057</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BS057 资产总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>asset_struct_BS000</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>BS000 流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>asset_struct_BS001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BS001 货币资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>asset_struct_BS002</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BS002 交易性金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>asset_struct_BS003</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BS003 衍生金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>asset_struct_BS004</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BS004 应收票据及应收账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>asset_struct_BS005</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BS005 应收票据</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>asset_struct_BS006</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>BS006 应收账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>asset_struct_BS007</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BS007 应收款项融资</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>asset_struct_BS008</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BS008 预付款项</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>asset_struct_BS009</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BS009 其他应收款(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>asset_struct_BS010</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BS010 应收股利</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>asset_struct_BS011</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BS011 应收利息</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>asset_struct_BS012</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BS012 其他应收款</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>asset_struct_BS013</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BS013 买入返售金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>asset_struct_BS014</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BS014 存货</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>asset_struct_BS015</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BS015 其中：消耗性生物资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>asset_struct_BS016</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BS016 合同资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>asset_struct_BS017</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BS017 划分为持有待售的资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>asset_struct_BS018</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BS018 一年内到期的非流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>asset_struct_BS019</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BS019 待摊费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>asset_struct_BS020</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BS020 其他流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>asset_struct_BS021</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BS021 其他金融类流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>asset_struct_BS022</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BS022 结算备付金</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>asset_struct_BS023</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BS023 拆出资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>asset_struct_BS024</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BS024 应收保费</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>asset_struct_BS025</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BS025 应收分保账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>asset_struct_BS026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BS026 应收分保合同准备金</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>asset_struct_BS027</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BS027 流动资产合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>asset_struct_BS028</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BS028 非流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>asset_struct_BS029</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BS029 发放贷款及垫款</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>asset_struct_BS030</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BS030 以公允价值且其变动计入其他综合收益的金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>asset_struct_BS031</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BS031 以摊余成本计量的金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>asset_struct_BS032</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BS032 债权投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>asset_struct_BS033</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BS033 其他债权投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>asset_struct_BS034</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BS034 可供出售金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>asset_struct_BS035</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BS035 其他权益工具投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>asset_struct_BS036</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>BS036 持有至到期投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>asset_struct_BS037</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BS037 其他非流动金融资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>asset_struct_BS038</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BS038 长期应收款</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>asset_struct_BS039</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>BS039 长期股权投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>asset_struct_BS040</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BS040 投资性房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>asset_struct_BS041</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BS041 固定资产(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>asset_struct_BS042</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BS042 固定资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>asset_struct_BS043</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BS043 固定资产清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>asset_struct_BS044</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>BS044 在建工程(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>asset_struct_BS045</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>BS045 在建工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>asset_struct_BS046</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BS046 工程物资</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>asset_struct_BS047</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>BS047 生产性生物资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>asset_struct_BS048</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BS048 油气资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>asset_struct_BS049</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BS049 使用权资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>asset_struct_BS050</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>BS050 无形资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>asset_struct_BS051</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BS051 开发支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>asset_struct_BS052</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BS052 商誉</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>asset_struct_BS053</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BS053 长期待摊费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>asset_struct_BS054</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BS054 递延所得税资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>asset_struct_BS055</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BS055 其他非流动资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>asset_struct_BS056</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>BS056 非流动资产合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>asset_struct_BS057</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>资产总计仅描述绝对量变化，不做占比分析。</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BS057 资产总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>liability_abs_BS058</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>BS058 流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>liability_abs_BS059</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BS059 短期借款</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>liability_abs_BS060</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BS060 交易性金融负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>liability_abs_BS061</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BS061 衍生金融负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>liability_abs_BS062</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BS062 应付票据及应付账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>liability_abs_BS063</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BS063 应付票据</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>liability_abs_BS064</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BS064 应付账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>liability_abs_BS065</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>BS065 预收款项</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>liability_abs_BS066</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BS066 合同负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>liability_abs_BS067</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BS067 应付手续费及佣金</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>liability_abs_BS068</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BS068 应付职工薪酬</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>liability_abs_BS069</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>BS069 应交税费</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>liability_abs_BS070</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>BS070 其他应付款(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>liability_abs_BS071</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>BS071 应付利息</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>liability_abs_BS072</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>BS072 应付股利</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>liability_abs_BS073</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>BS073 其他应付款</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>liability_abs_BS074</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>BS074 划分为持有待售的负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>liability_abs_BS075</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>BS075 一年内到期的非流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>liability_abs_BS076</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>BS076 预提费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>liability_abs_BS077</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>BS077 递延收益-流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>liability_abs_BS078</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>BS078 应付短期债券</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>liability_abs_BS079</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>BS079 其他流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>liability_abs_BS080</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>BS080 其他金融类流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>liability_abs_BS081</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>BS081 向中央银行借款</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>liability_abs_BS082</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>BS082 吸收存款及同业存放</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>liability_abs_BS083</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>BS083 拆入资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>liability_abs_BS084</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>BS084 卖出回购金融资产款</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>liability_abs_BS085</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>BS085 应付分保账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>liability_abs_BS086</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>BS086 保险合同准备金</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>liability_abs_BS087</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>BS087 代理买卖证券款</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>liability_abs_BS088</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BS088 代理承销证券款</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>liability_abs_BS089</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BS089 流动负债合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>liability_abs_BS090</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BS090 非流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>liability_abs_BS091</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>BS091 长期借款</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>liability_abs_BS092</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>BS092 应付债券</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>liability_abs_BS093</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>BS093 租赁负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>liability_abs_BS094</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>BS094 长期应付款(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>liability_abs_BS095</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>BS095 长期应付款</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>liability_abs_BS096</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>BS096 专项应付款</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>liability_abs_BS097</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>BS097 长期应付职工薪酬</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>liability_abs_BS098</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BS098 预计负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>liability_abs_BS099</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BS099 递延所得税负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>liability_abs_BS100</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>BS100 递延收益-非流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>liability_abs_BS101</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BS101 其他非流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>liability_abs_BS102</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BS102 非流动负债合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>liability_abs_BS103</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BS103 负债合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>liability_struct_BS058</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>BS058 流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>liability_struct_BS059</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>BS059 短期借款</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>liability_struct_BS060</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BS060 交易性金融负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>liability_struct_BS061</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>BS061 衍生金融负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>liability_struct_BS062</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BS062 应付票据及应付账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>liability_struct_BS063</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BS063 应付票据</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>liability_struct_BS064</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>BS064 应付账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>liability_struct_BS065</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>BS065 预收款项</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>liability_struct_BS066</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>BS066 合同负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>liability_struct_BS067</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BS067 应付手续费及佣金</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>liability_struct_BS068</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BS068 应付职工薪酬</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>liability_struct_BS069</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>BS069 应交税费</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>liability_struct_BS070</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BS070 其他应付款(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>liability_struct_BS071</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>BS071 应付利息</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>liability_struct_BS072</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>BS072 应付股利</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>liability_struct_BS073</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>BS073 其他应付款</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>liability_struct_BS074</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BS074 划分为持有待售的负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>liability_struct_BS075</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>BS075 一年内到期的非流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>liability_struct_BS076</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BS076 预提费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>liability_struct_BS077</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>BS077 递延收益-流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>liability_struct_BS078</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>BS078 应付短期债券</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>liability_struct_BS079</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>BS079 其他流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>liability_struct_BS080</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>BS080 其他金融类流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>liability_struct_BS081</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>BS081 向中央银行借款</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>liability_struct_BS082</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BS082 吸收存款及同业存放</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>liability_struct_BS083</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>BS083 拆入资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>liability_struct_BS084</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>BS084 卖出回购金融资产款</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>liability_struct_BS085</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BS085 应付分保账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>liability_struct_BS086</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BS086 保险合同准备金</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>liability_struct_BS087</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>BS087 代理买卖证券款</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>liability_struct_BS088</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>BS088 代理承销证券款</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>liability_struct_BS089</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BS089 流动负债合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>liability_struct_BS090</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>BS090 非流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>liability_struct_BS091</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>BS091 长期借款</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>liability_struct_BS092</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BS092 应付债券</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>liability_struct_BS093</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>BS093 租赁负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>liability_struct_BS094</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>BS094 长期应付款(合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>liability_struct_BS095</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BS095 长期应付款</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>liability_struct_BS096</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BS096 专项应付款</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>liability_struct_BS097</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>BS097 长期应付职工薪酬</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>liability_struct_BS098</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>BS098 预计负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>liability_struct_BS099</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>BS099 递延所得税负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>liability_struct_BS100</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>BS100 递延收益-非流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>liability_struct_BS101</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BS101 其他非流动负债</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>liability_struct_BS102</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>BS102 非流动负债合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>liability_struct_BS103</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>负债合计仅描述绝对量变化，不做占比分析。</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>BS103 负债合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>scale_phrase_up</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>增加{abs_pct}%</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>绝对量变化词-增加</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>scale_phrase_down</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>减少{abs_pct}%</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>绝对量变化词-减少</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>scale_phrase_stable</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>保持稳定（变动{abs_pct}%）</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>绝对量变化词-稳定</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>struct_phrase_up</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>上升{abs_pp}个百分点</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>结构变化词-上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>struct_phrase_down</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>下降{abs_pp}个百分点</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>结构变化词-下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>struct_phrase_stable</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>基本稳定（变动{abs_pp}个百分点）</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>结构变化词-稳定</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/rulebook.xlsx
+++ b/config/rulebook.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指标别名映射" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务比率规则" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis_text_templates" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis_thresholds" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1887,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1909,10 +1910,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>variables</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1929,10 +1935,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>???????</t>
         </is>
@@ -1949,10 +1960,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>???????</t>
         </is>
@@ -1969,10 +1985,10 @@
           <t>资产总计仅描述绝对量变化，不做占比分析。</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>????????</t>
         </is>
@@ -1989,10 +2005,15 @@
           <t>占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>??/???????</t>
         </is>
@@ -2009,10 +2030,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
@@ -2029,10 +2055,10 @@
           <t>负债合计仅描述绝对量变化，不做占比分析。</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>????????</t>
         </is>
@@ -2049,10 +2075,15 @@
           <t>占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>??/???????</t>
         </is>
@@ -2069,10 +2100,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
@@ -2089,10 +2125,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>BS000 流动资产</t>
         </is>
@@ -2109,10 +2150,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>BS001 货币资金</t>
         </is>
@@ -2129,10 +2175,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>BS002 交易性金融资产</t>
         </is>
@@ -2149,10 +2200,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>BS003 衍生金融资产</t>
         </is>
@@ -2169,10 +2225,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>BS004 应收票据及应收账款</t>
         </is>
@@ -2189,10 +2250,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>BS005 应收票据</t>
         </is>
@@ -2209,10 +2275,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>BS006 应收账款</t>
         </is>
@@ -2229,10 +2300,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>BS007 应收款项融资</t>
         </is>
@@ -2249,10 +2325,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>BS008 预付款项</t>
         </is>
@@ -2269,10 +2350,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>BS009 其他应收款(合计</t>
         </is>
@@ -2289,10 +2375,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>BS010 应收股利</t>
         </is>
@@ -2309,10 +2400,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>BS011 应收利息</t>
         </is>
@@ -2329,10 +2425,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>BS012 其他应收款</t>
         </is>
@@ -2349,10 +2450,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>BS013 买入返售金融资产</t>
         </is>
@@ -2369,10 +2475,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>BS014 存货</t>
         </is>
@@ -2389,10 +2500,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>BS015 其中：消耗性生物资产</t>
         </is>
@@ -2409,10 +2525,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>BS016 合同资产</t>
         </is>
@@ -2429,10 +2550,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>BS017 划分为持有待售的资产</t>
         </is>
@@ -2449,10 +2575,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>BS018 一年内到期的非流动资产</t>
         </is>
@@ -2469,10 +2600,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>BS019 待摊费用</t>
         </is>
@@ -2489,10 +2625,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>BS020 其他流动资产</t>
         </is>
@@ -2509,10 +2650,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>BS021 其他金融类流动资产</t>
         </is>
@@ -2529,10 +2675,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>BS022 结算备付金</t>
         </is>
@@ -2549,10 +2700,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>BS023 拆出资金</t>
         </is>
@@ -2569,10 +2725,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>BS024 应收保费</t>
         </is>
@@ -2589,10 +2750,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>BS025 应收分保账款</t>
         </is>
@@ -2609,10 +2775,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>BS026 应收分保合同准备金</t>
         </is>
@@ -2629,10 +2800,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>BS027 流动资产合计</t>
         </is>
@@ -2649,10 +2825,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>BS028 非流动资产</t>
         </is>
@@ -2669,10 +2850,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>BS029 发放贷款及垫款</t>
         </is>
@@ -2689,10 +2875,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>BS030 以公允价值且其变动计入其他综合收益的金融资产</t>
         </is>
@@ -2709,10 +2900,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>BS031 以摊余成本计量的金融资产</t>
         </is>
@@ -2729,10 +2925,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>BS032 债权投资</t>
         </is>
@@ -2749,10 +2950,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>BS033 其他债权投资</t>
         </is>
@@ -2769,10 +2975,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>BS034 可供出售金融资产</t>
         </is>
@@ -2789,10 +3000,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>BS035 其他权益工具投资</t>
         </is>
@@ -2809,10 +3025,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>BS036 持有至到期投资</t>
         </is>
@@ -2829,10 +3050,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>BS037 其他非流动金融资产</t>
         </is>
@@ -2849,10 +3075,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>BS038 长期应收款</t>
         </is>
@@ -2869,10 +3100,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>BS039 长期股权投资</t>
         </is>
@@ -2889,10 +3125,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>BS040 投资性房地产</t>
         </is>
@@ -2909,10 +3150,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>BS041 固定资产(合计</t>
         </is>
@@ -2929,10 +3175,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>BS042 固定资产</t>
         </is>
@@ -2949,10 +3200,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>BS043 固定资产清理</t>
         </is>
@@ -2969,10 +3225,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>BS044 在建工程(合计</t>
         </is>
@@ -2989,10 +3250,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>BS045 在建工程</t>
         </is>
@@ -3009,10 +3275,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>BS046 工程物资</t>
         </is>
@@ -3029,10 +3300,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>BS047 生产性生物资产</t>
         </is>
@@ -3049,10 +3325,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>BS048 油气资产</t>
         </is>
@@ -3069,10 +3350,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>BS049 使用权资产</t>
         </is>
@@ -3089,10 +3375,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>BS050 无形资产</t>
         </is>
@@ -3109,10 +3400,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>BS051 开发支出</t>
         </is>
@@ -3129,10 +3425,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>BS052 商誉</t>
         </is>
@@ -3149,10 +3450,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>BS053 长期待摊费用</t>
         </is>
@@ -3169,10 +3475,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>BS054 递延所得税资产</t>
         </is>
@@ -3189,10 +3500,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>BS055 其他非流动资产</t>
         </is>
@@ -3209,10 +3525,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>BS056 非流动资产合计</t>
         </is>
@@ -3229,10 +3550,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>BS057 资产总计</t>
         </is>
@@ -3249,10 +3575,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>BS000 流动资产</t>
         </is>
@@ -3269,10 +3600,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>BS001 货币资金</t>
         </is>
@@ -3289,10 +3625,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>BS002 交易性金融资产</t>
         </is>
@@ -3309,10 +3650,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>BS003 衍生金融资产</t>
         </is>
@@ -3329,10 +3675,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>BS004 应收票据及应收账款</t>
         </is>
@@ -3349,10 +3700,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>BS005 应收票据</t>
         </is>
@@ -3369,10 +3725,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>BS006 应收账款</t>
         </is>
@@ -3389,10 +3750,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>BS007 应收款项融资</t>
         </is>
@@ -3409,10 +3775,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>BS008 预付款项</t>
         </is>
@@ -3429,10 +3800,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>BS009 其他应收款(合计</t>
         </is>
@@ -3449,10 +3825,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>BS010 应收股利</t>
         </is>
@@ -3469,10 +3850,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>BS011 应收利息</t>
         </is>
@@ -3489,10 +3875,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
         <is>
           <t>BS012 其他应收款</t>
         </is>
@@ -3509,10 +3900,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>BS013 买入返售金融资产</t>
         </is>
@@ -3529,10 +3925,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>BS014 存货</t>
         </is>
@@ -3549,10 +3950,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
         <is>
           <t>BS015 其中：消耗性生物资产</t>
         </is>
@@ -3569,10 +3975,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>BS016 合同资产</t>
         </is>
@@ -3589,10 +4000,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>BS017 划分为持有待售的资产</t>
         </is>
@@ -3609,10 +4025,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>BS018 一年内到期的非流动资产</t>
         </is>
@@ -3629,10 +4050,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>BS019 待摊费用</t>
         </is>
@@ -3649,10 +4075,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
         <is>
           <t>BS020 其他流动资产</t>
         </is>
@@ -3669,10 +4100,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t>BS021 其他金融类流动资产</t>
         </is>
@@ -3689,10 +4125,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t>BS022 结算备付金</t>
         </is>
@@ -3709,10 +4150,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>BS023 拆出资金</t>
         </is>
@@ -3729,10 +4175,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
         <is>
           <t>BS024 应收保费</t>
         </is>
@@ -3749,10 +4200,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="inlineStr">
         <is>
           <t>BS025 应收分保账款</t>
         </is>
@@ -3769,10 +4225,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>BS026 应收分保合同准备金</t>
         </is>
@@ -3789,10 +4250,15 @@
           <t>占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t>BS027 流动资产合计</t>
         </is>
@@ -3809,10 +4275,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>BS028 非流动资产</t>
         </is>
@@ -3829,10 +4300,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>BS029 发放贷款及垫款</t>
         </is>
@@ -3849,10 +4325,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>BS030 以公允价值且其变动计入其他综合收益的金融资产</t>
         </is>
@@ -3869,10 +4350,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>BS031 以摊余成本计量的金融资产</t>
         </is>
@@ -3889,10 +4375,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>BS032 债权投资</t>
         </is>
@@ -3909,10 +4400,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="inlineStr">
         <is>
           <t>BS033 其他债权投资</t>
         </is>
@@ -3929,10 +4425,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" t="inlineStr">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>BS034 可供出售金融资产</t>
         </is>
@@ -3949,10 +4450,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="inlineStr">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
         <is>
           <t>BS035 其他权益工具投资</t>
         </is>
@@ -3969,10 +4475,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>BS036 持有至到期投资</t>
         </is>
@@ -3989,10 +4500,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>BS037 其他非流动金融资产</t>
         </is>
@@ -4009,10 +4525,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>BS038 长期应收款</t>
         </is>
@@ -4029,10 +4550,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
         <is>
           <t>BS039 长期股权投资</t>
         </is>
@@ -4049,10 +4575,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
         <is>
           <t>BS040 投资性房地产</t>
         </is>
@@ -4069,10 +4600,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>1</v>
-      </c>
-      <c r="D109" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>BS041 固定资产(合计</t>
         </is>
@@ -4089,10 +4625,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>1</v>
-      </c>
-      <c r="D110" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
         <is>
           <t>BS042 固定资产</t>
         </is>
@@ -4109,10 +4650,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" t="inlineStr">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
         <is>
           <t>BS043 固定资产清理</t>
         </is>
@@ -4129,10 +4675,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" t="inlineStr">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="inlineStr">
         <is>
           <t>BS044 在建工程(合计</t>
         </is>
@@ -4149,10 +4700,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C113" t="n">
-        <v>1</v>
-      </c>
-      <c r="D113" t="inlineStr">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
         <is>
           <t>BS045 在建工程</t>
         </is>
@@ -4169,10 +4725,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" t="inlineStr">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
         <is>
           <t>BS046 工程物资</t>
         </is>
@@ -4189,10 +4750,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>1</v>
-      </c>
-      <c r="D115" t="inlineStr">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
         <is>
           <t>BS047 生产性生物资产</t>
         </is>
@@ -4209,10 +4775,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v>1</v>
-      </c>
-      <c r="D116" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
         <is>
           <t>BS048 油气资产</t>
         </is>
@@ -4229,10 +4800,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>1</v>
-      </c>
-      <c r="D117" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="inlineStr">
         <is>
           <t>BS049 使用权资产</t>
         </is>
@@ -4249,10 +4825,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v>1</v>
-      </c>
-      <c r="D118" t="inlineStr">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="inlineStr">
         <is>
           <t>BS050 无形资产</t>
         </is>
@@ -4269,10 +4850,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C119" t="n">
-        <v>1</v>
-      </c>
-      <c r="D119" t="inlineStr">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
         <is>
           <t>BS051 开发支出</t>
         </is>
@@ -4289,10 +4875,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>1</v>
-      </c>
-      <c r="D120" t="inlineStr">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
         <is>
           <t>BS052 商誉</t>
         </is>
@@ -4309,10 +4900,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>1</v>
-      </c>
-      <c r="D121" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
         <is>
           <t>BS053 长期待摊费用</t>
         </is>
@@ -4329,10 +4925,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>1</v>
-      </c>
-      <c r="D122" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
         <is>
           <t>BS054 递延所得税资产</t>
         </is>
@@ -4349,10 +4950,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C123" t="n">
-        <v>1</v>
-      </c>
-      <c r="D123" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
         <is>
           <t>BS055 其他非流动资产</t>
         </is>
@@ -4369,10 +4975,15 @@
           <t>占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" t="inlineStr">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
         <is>
           <t>BS056 非流动资产合计</t>
         </is>
@@ -4389,10 +5000,10 @@
           <t>资产总计仅描述绝对量变化，不做占比分析。</t>
         </is>
       </c>
-      <c r="C125" t="n">
-        <v>1</v>
-      </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
         <is>
           <t>BS057 资产总计</t>
         </is>
@@ -4409,10 +5020,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>1</v>
-      </c>
-      <c r="D126" t="inlineStr">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>BS058 流动负债</t>
         </is>
@@ -4429,10 +5045,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C127" t="n">
-        <v>1</v>
-      </c>
-      <c r="D127" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
         <is>
           <t>BS059 短期借款</t>
         </is>
@@ -4449,10 +5070,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t>BS060 交易性金融负债</t>
         </is>
@@ -4469,10 +5095,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>1</v>
-      </c>
-      <c r="D129" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>BS061 衍生金融负债</t>
         </is>
@@ -4489,10 +5120,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v>1</v>
-      </c>
-      <c r="D130" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
         <is>
           <t>BS062 应付票据及应付账款</t>
         </is>
@@ -4509,10 +5145,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C131" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
         <is>
           <t>BS063 应付票据</t>
         </is>
@@ -4529,10 +5170,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
         <is>
           <t>BS064 应付账款</t>
         </is>
@@ -4549,10 +5195,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>1</v>
-      </c>
-      <c r="D133" t="inlineStr">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t>BS065 预收款项</t>
         </is>
@@ -4569,10 +5220,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v>1</v>
-      </c>
-      <c r="D134" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
         <is>
           <t>BS066 合同负债</t>
         </is>
@@ -4589,10 +5245,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
         <is>
           <t>BS067 应付手续费及佣金</t>
         </is>
@@ -4609,10 +5270,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" t="inlineStr">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
         <is>
           <t>BS068 应付职工薪酬</t>
         </is>
@@ -4629,10 +5295,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" t="inlineStr">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>BS069 应交税费</t>
         </is>
@@ -4649,10 +5320,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C138" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" t="inlineStr">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
         <is>
           <t>BS070 其他应付款(合计</t>
         </is>
@@ -4669,10 +5345,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C139" t="n">
-        <v>1</v>
-      </c>
-      <c r="D139" t="inlineStr">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="inlineStr">
         <is>
           <t>BS071 应付利息</t>
         </is>
@@ -4689,10 +5370,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
         <is>
           <t>BS072 应付股利</t>
         </is>
@@ -4709,10 +5395,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C141" t="n">
-        <v>1</v>
-      </c>
-      <c r="D141" t="inlineStr">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
         <is>
           <t>BS073 其他应付款</t>
         </is>
@@ -4729,10 +5420,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>1</v>
-      </c>
-      <c r="D142" t="inlineStr">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
         <is>
           <t>BS074 划分为持有待售的负债</t>
         </is>
@@ -4749,10 +5445,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C143" t="n">
-        <v>1</v>
-      </c>
-      <c r="D143" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
         <is>
           <t>BS075 一年内到期的非流动负债</t>
         </is>
@@ -4769,10 +5470,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C144" t="n">
-        <v>1</v>
-      </c>
-      <c r="D144" t="inlineStr">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
         <is>
           <t>BS076 预提费用</t>
         </is>
@@ -4789,10 +5495,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C145" t="n">
-        <v>1</v>
-      </c>
-      <c r="D145" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
         <is>
           <t>BS077 递延收益-流动负债</t>
         </is>
@@ -4809,10 +5520,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C146" t="n">
-        <v>1</v>
-      </c>
-      <c r="D146" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
         <is>
           <t>BS078 应付短期债券</t>
         </is>
@@ -4829,10 +5545,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C147" t="n">
-        <v>1</v>
-      </c>
-      <c r="D147" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
         <is>
           <t>BS079 其他流动负债</t>
         </is>
@@ -4849,10 +5570,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C148" t="n">
-        <v>1</v>
-      </c>
-      <c r="D148" t="inlineStr">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
         <is>
           <t>BS080 其他金融类流动负债</t>
         </is>
@@ -4869,10 +5595,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C149" t="n">
-        <v>1</v>
-      </c>
-      <c r="D149" t="inlineStr">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
         <is>
           <t>BS081 向中央银行借款</t>
         </is>
@@ -4889,10 +5620,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C150" t="n">
-        <v>1</v>
-      </c>
-      <c r="D150" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
         <is>
           <t>BS082 吸收存款及同业存放</t>
         </is>
@@ -4909,10 +5645,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C151" t="n">
-        <v>1</v>
-      </c>
-      <c r="D151" t="inlineStr">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="inlineStr">
         <is>
           <t>BS083 拆入资金</t>
         </is>
@@ -4929,10 +5670,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" t="inlineStr">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr">
         <is>
           <t>BS084 卖出回购金融资产款</t>
         </is>
@@ -4949,10 +5695,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C153" t="n">
-        <v>1</v>
-      </c>
-      <c r="D153" t="inlineStr">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="inlineStr">
         <is>
           <t>BS085 应付分保账款</t>
         </is>
@@ -4969,10 +5720,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>1</v>
-      </c>
-      <c r="D154" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="inlineStr">
         <is>
           <t>BS086 保险合同准备金</t>
         </is>
@@ -4989,10 +5745,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C155" t="n">
-        <v>1</v>
-      </c>
-      <c r="D155" t="inlineStr">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="inlineStr">
         <is>
           <t>BS087 代理买卖证券款</t>
         </is>
@@ -5009,10 +5770,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C156" t="n">
-        <v>1</v>
-      </c>
-      <c r="D156" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="inlineStr">
         <is>
           <t>BS088 代理承销证券款</t>
         </is>
@@ -5029,10 +5795,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C157" t="n">
-        <v>1</v>
-      </c>
-      <c r="D157" t="inlineStr">
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="inlineStr">
         <is>
           <t>BS089 流动负债合计</t>
         </is>
@@ -5049,10 +5820,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>1</v>
-      </c>
-      <c r="D158" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr">
         <is>
           <t>BS090 非流动负债</t>
         </is>
@@ -5069,10 +5845,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C159" t="n">
-        <v>1</v>
-      </c>
-      <c r="D159" t="inlineStr">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="inlineStr">
         <is>
           <t>BS091 长期借款</t>
         </is>
@@ -5089,10 +5870,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C160" t="n">
-        <v>1</v>
-      </c>
-      <c r="D160" t="inlineStr">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="inlineStr">
         <is>
           <t>BS092 应付债券</t>
         </is>
@@ -5109,10 +5895,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C161" t="n">
-        <v>1</v>
-      </c>
-      <c r="D161" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="inlineStr">
         <is>
           <t>BS093 租赁负债</t>
         </is>
@@ -5129,10 +5920,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C162" t="n">
-        <v>1</v>
-      </c>
-      <c r="D162" t="inlineStr">
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="inlineStr">
         <is>
           <t>BS094 长期应付款(合计</t>
         </is>
@@ -5149,10 +5945,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C163" t="n">
-        <v>1</v>
-      </c>
-      <c r="D163" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="inlineStr">
         <is>
           <t>BS095 长期应付款</t>
         </is>
@@ -5169,10 +5970,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C164" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" t="inlineStr">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="inlineStr">
         <is>
           <t>BS096 专项应付款</t>
         </is>
@@ -5189,10 +5995,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C165" t="n">
-        <v>1</v>
-      </c>
-      <c r="D165" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="inlineStr">
         <is>
           <t>BS097 长期应付职工薪酬</t>
         </is>
@@ -5209,10 +6020,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C166" t="n">
-        <v>1</v>
-      </c>
-      <c r="D166" t="inlineStr">
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr">
         <is>
           <t>BS098 预计负债</t>
         </is>
@@ -5229,10 +6045,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D167" t="inlineStr">
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="inlineStr">
         <is>
           <t>BS099 递延所得税负债</t>
         </is>
@@ -5249,10 +6070,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C168" t="n">
-        <v>1</v>
-      </c>
-      <c r="D168" t="inlineStr">
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="inlineStr">
         <is>
           <t>BS100 递延收益-非流动负债</t>
         </is>
@@ -5269,10 +6095,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C169" t="n">
-        <v>1</v>
-      </c>
-      <c r="D169" t="inlineStr">
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="inlineStr">
         <is>
           <t>BS101 其他非流动负债</t>
         </is>
@@ -5289,10 +6120,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C170" t="n">
-        <v>1</v>
-      </c>
-      <c r="D170" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="inlineStr">
         <is>
           <t>BS102 非流动负债合计</t>
         </is>
@@ -5309,10 +6145,15 @@
           <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
-      <c r="C171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D171" t="inlineStr">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="inlineStr">
         <is>
           <t>BS103 负债合计</t>
         </is>
@@ -5329,10 +6170,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C172" t="n">
-        <v>1</v>
-      </c>
-      <c r="D172" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="inlineStr">
         <is>
           <t>BS058 流动负债</t>
         </is>
@@ -5349,10 +6195,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C173" t="n">
-        <v>1</v>
-      </c>
-      <c r="D173" t="inlineStr">
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr">
         <is>
           <t>BS059 短期借款</t>
         </is>
@@ -5369,10 +6220,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C174" t="n">
-        <v>1</v>
-      </c>
-      <c r="D174" t="inlineStr">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="inlineStr">
         <is>
           <t>BS060 交易性金融负债</t>
         </is>
@@ -5389,10 +6245,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C175" t="n">
-        <v>1</v>
-      </c>
-      <c r="D175" t="inlineStr">
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="inlineStr">
         <is>
           <t>BS061 衍生金融负债</t>
         </is>
@@ -5409,10 +6270,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C176" t="n">
-        <v>1</v>
-      </c>
-      <c r="D176" t="inlineStr">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="inlineStr">
         <is>
           <t>BS062 应付票据及应付账款</t>
         </is>
@@ -5429,10 +6295,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C177" t="n">
-        <v>1</v>
-      </c>
-      <c r="D177" t="inlineStr">
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="inlineStr">
         <is>
           <t>BS063 应付票据</t>
         </is>
@@ -5449,10 +6320,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C178" t="n">
-        <v>1</v>
-      </c>
-      <c r="D178" t="inlineStr">
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="inlineStr">
         <is>
           <t>BS064 应付账款</t>
         </is>
@@ -5469,10 +6345,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C179" t="n">
-        <v>1</v>
-      </c>
-      <c r="D179" t="inlineStr">
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="inlineStr">
         <is>
           <t>BS065 预收款项</t>
         </is>
@@ -5489,10 +6370,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C180" t="n">
-        <v>1</v>
-      </c>
-      <c r="D180" t="inlineStr">
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="inlineStr">
         <is>
           <t>BS066 合同负债</t>
         </is>
@@ -5509,10 +6395,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C181" t="n">
-        <v>1</v>
-      </c>
-      <c r="D181" t="inlineStr">
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="inlineStr">
         <is>
           <t>BS067 应付手续费及佣金</t>
         </is>
@@ -5529,10 +6420,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C182" t="n">
-        <v>1</v>
-      </c>
-      <c r="D182" t="inlineStr">
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="inlineStr">
         <is>
           <t>BS068 应付职工薪酬</t>
         </is>
@@ -5549,10 +6445,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C183" t="n">
-        <v>1</v>
-      </c>
-      <c r="D183" t="inlineStr">
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="inlineStr">
         <is>
           <t>BS069 应交税费</t>
         </is>
@@ -5569,10 +6470,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C184" t="n">
-        <v>1</v>
-      </c>
-      <c r="D184" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="inlineStr">
         <is>
           <t>BS070 其他应付款(合计</t>
         </is>
@@ -5589,10 +6495,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C185" t="n">
-        <v>1</v>
-      </c>
-      <c r="D185" t="inlineStr">
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="inlineStr">
         <is>
           <t>BS071 应付利息</t>
         </is>
@@ -5609,10 +6520,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C186" t="n">
-        <v>1</v>
-      </c>
-      <c r="D186" t="inlineStr">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="inlineStr">
         <is>
           <t>BS072 应付股利</t>
         </is>
@@ -5629,10 +6545,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C187" t="n">
-        <v>1</v>
-      </c>
-      <c r="D187" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="inlineStr">
         <is>
           <t>BS073 其他应付款</t>
         </is>
@@ -5649,10 +6570,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C188" t="n">
-        <v>1</v>
-      </c>
-      <c r="D188" t="inlineStr">
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="inlineStr">
         <is>
           <t>BS074 划分为持有待售的负债</t>
         </is>
@@ -5669,10 +6595,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C189" t="n">
-        <v>1</v>
-      </c>
-      <c r="D189" t="inlineStr">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="inlineStr">
         <is>
           <t>BS075 一年内到期的非流动负债</t>
         </is>
@@ -5689,10 +6620,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C190" t="n">
-        <v>1</v>
-      </c>
-      <c r="D190" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="inlineStr">
         <is>
           <t>BS076 预提费用</t>
         </is>
@@ -5709,10 +6645,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C191" t="n">
-        <v>1</v>
-      </c>
-      <c r="D191" t="inlineStr">
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="inlineStr">
         <is>
           <t>BS077 递延收益-流动负债</t>
         </is>
@@ -5729,10 +6670,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C192" t="n">
-        <v>1</v>
-      </c>
-      <c r="D192" t="inlineStr">
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="inlineStr">
         <is>
           <t>BS078 应付短期债券</t>
         </is>
@@ -5749,10 +6695,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C193" t="n">
-        <v>1</v>
-      </c>
-      <c r="D193" t="inlineStr">
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="inlineStr">
         <is>
           <t>BS079 其他流动负债</t>
         </is>
@@ -5769,10 +6720,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C194" t="n">
-        <v>1</v>
-      </c>
-      <c r="D194" t="inlineStr">
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="inlineStr">
         <is>
           <t>BS080 其他金融类流动负债</t>
         </is>
@@ -5789,10 +6745,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C195" t="n">
-        <v>1</v>
-      </c>
-      <c r="D195" t="inlineStr">
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="inlineStr">
         <is>
           <t>BS081 向中央银行借款</t>
         </is>
@@ -5809,10 +6770,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C196" t="n">
-        <v>1</v>
-      </c>
-      <c r="D196" t="inlineStr">
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="inlineStr">
         <is>
           <t>BS082 吸收存款及同业存放</t>
         </is>
@@ -5829,10 +6795,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C197" t="n">
-        <v>1</v>
-      </c>
-      <c r="D197" t="inlineStr">
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="inlineStr">
         <is>
           <t>BS083 拆入资金</t>
         </is>
@@ -5849,10 +6820,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C198" t="n">
-        <v>1</v>
-      </c>
-      <c r="D198" t="inlineStr">
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="inlineStr">
         <is>
           <t>BS084 卖出回购金融资产款</t>
         </is>
@@ -5869,10 +6845,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C199" t="n">
-        <v>1</v>
-      </c>
-      <c r="D199" t="inlineStr">
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="inlineStr">
         <is>
           <t>BS085 应付分保账款</t>
         </is>
@@ -5889,10 +6870,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C200" t="n">
-        <v>1</v>
-      </c>
-      <c r="D200" t="inlineStr">
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="inlineStr">
         <is>
           <t>BS086 保险合同准备金</t>
         </is>
@@ -5909,10 +6895,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C201" t="n">
-        <v>1</v>
-      </c>
-      <c r="D201" t="inlineStr">
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="inlineStr">
         <is>
           <t>BS087 代理买卖证券款</t>
         </is>
@@ -5929,10 +6920,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C202" t="n">
-        <v>1</v>
-      </c>
-      <c r="D202" t="inlineStr">
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="inlineStr">
         <is>
           <t>BS088 代理承销证券款</t>
         </is>
@@ -5949,10 +6945,15 @@
           <t>占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C203" t="n">
-        <v>1</v>
-      </c>
-      <c r="D203" t="inlineStr">
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="inlineStr">
         <is>
           <t>BS089 流动负债合计</t>
         </is>
@@ -5969,10 +6970,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C204" t="n">
-        <v>1</v>
-      </c>
-      <c r="D204" t="inlineStr">
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="inlineStr">
         <is>
           <t>BS090 非流动负债</t>
         </is>
@@ -5989,10 +6995,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C205" t="n">
-        <v>1</v>
-      </c>
-      <c r="D205" t="inlineStr">
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr">
         <is>
           <t>BS091 长期借款</t>
         </is>
@@ -6009,10 +7020,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C206" t="n">
-        <v>1</v>
-      </c>
-      <c r="D206" t="inlineStr">
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr">
         <is>
           <t>BS092 应付债券</t>
         </is>
@@ -6029,10 +7045,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C207" t="n">
-        <v>1</v>
-      </c>
-      <c r="D207" t="inlineStr">
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="inlineStr">
         <is>
           <t>BS093 租赁负债</t>
         </is>
@@ -6049,10 +7070,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C208" t="n">
-        <v>1</v>
-      </c>
-      <c r="D208" t="inlineStr">
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="inlineStr">
         <is>
           <t>BS094 长期应付款(合计</t>
         </is>
@@ -6069,10 +7095,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C209" t="n">
-        <v>1</v>
-      </c>
-      <c r="D209" t="inlineStr">
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="inlineStr">
         <is>
           <t>BS095 长期应付款</t>
         </is>
@@ -6089,10 +7120,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C210" t="n">
-        <v>1</v>
-      </c>
-      <c r="D210" t="inlineStr">
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="inlineStr">
         <is>
           <t>BS096 专项应付款</t>
         </is>
@@ -6109,10 +7145,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C211" t="n">
-        <v>1</v>
-      </c>
-      <c r="D211" t="inlineStr">
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="inlineStr">
         <is>
           <t>BS097 长期应付职工薪酬</t>
         </is>
@@ -6129,10 +7170,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C212" t="n">
-        <v>1</v>
-      </c>
-      <c r="D212" t="inlineStr">
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="inlineStr">
         <is>
           <t>BS098 预计负债</t>
         </is>
@@ -6149,10 +7195,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C213" t="n">
-        <v>1</v>
-      </c>
-      <c r="D213" t="inlineStr">
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="inlineStr">
         <is>
           <t>BS099 递延所得税负债</t>
         </is>
@@ -6169,10 +7220,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C214" t="n">
-        <v>1</v>
-      </c>
-      <c r="D214" t="inlineStr">
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
         <is>
           <t>BS100 递延收益-非流动负债</t>
         </is>
@@ -6189,10 +7245,15 @@
           <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C215" t="n">
-        <v>1</v>
-      </c>
-      <c r="D215" t="inlineStr">
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="inlineStr">
         <is>
           <t>BS101 其他非流动负债</t>
         </is>
@@ -6209,10 +7270,15 @@
           <t>占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
         </is>
       </c>
-      <c r="C216" t="n">
-        <v>1</v>
-      </c>
-      <c r="D216" t="inlineStr">
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="inlineStr">
         <is>
           <t>BS102 非流动负债合计</t>
         </is>
@@ -6229,10 +7295,10 @@
           <t>负债合计仅描述绝对量变化，不做占比分析。</t>
         </is>
       </c>
-      <c r="C217" t="n">
-        <v>1</v>
-      </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="inlineStr">
         <is>
           <t>BS103 负债合计</t>
         </is>
@@ -6249,10 +7315,15 @@
           <t>增加{abs_pct}%</t>
         </is>
       </c>
-      <c r="C218" t="n">
-        <v>1</v>
-      </c>
-      <c r="D218" t="inlineStr">
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>abs_pct</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="inlineStr">
         <is>
           <t>绝对量变化词-增加</t>
         </is>
@@ -6269,10 +7340,15 @@
           <t>减少{abs_pct}%</t>
         </is>
       </c>
-      <c r="C219" t="n">
-        <v>1</v>
-      </c>
-      <c r="D219" t="inlineStr">
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>abs_pct</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr">
         <is>
           <t>绝对量变化词-减少</t>
         </is>
@@ -6289,10 +7365,15 @@
           <t>保持稳定（变动{abs_pct}%）</t>
         </is>
       </c>
-      <c r="C220" t="n">
-        <v>1</v>
-      </c>
-      <c r="D220" t="inlineStr">
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>abs_pct</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
         <is>
           <t>绝对量变化词-稳定</t>
         </is>
@@ -6309,10 +7390,15 @@
           <t>上升{abs_pp}个百分点</t>
         </is>
       </c>
-      <c r="C221" t="n">
-        <v>1</v>
-      </c>
-      <c r="D221" t="inlineStr">
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>abs_pp</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="inlineStr">
         <is>
           <t>结构变化词-上升</t>
         </is>
@@ -6329,10 +7415,15 @@
           <t>下降{abs_pp}个百分点</t>
         </is>
       </c>
-      <c r="C222" t="n">
-        <v>1</v>
-      </c>
-      <c r="D222" t="inlineStr">
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>abs_pp</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="inlineStr">
         <is>
           <t>结构变化词-下降</t>
         </is>
@@ -6349,12 +7440,85 @@
           <t>基本稳定（变动{abs_pp}个百分点）</t>
         </is>
       </c>
-      <c r="C223" t="n">
-        <v>1</v>
-      </c>
-      <c r="D223" t="inlineStr">
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>abs_pp</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
         <is>
           <t>结构变化词-稳定</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>subject_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scale_stable_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>struct_stable_pp</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>全局默认阈值</t>
         </is>
       </c>
     </row>

--- a/config/rulebook.xlsx
+++ b/config/rulebook.xlsx
@@ -1888,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7451,6 +7451,533 @@
       <c r="E223" t="inlineStr">
         <is>
           <t>结构变化词-稳定</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>summary_abs_line</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>{name}?{y1}?{v1}???{y2}?{v2}???{y3}?{v3}???{y2}?{y1}{p21}?{y3}?{y2}{p32}?</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>????-???</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>summary_ratio_line</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>{name}?{base_name}???{y1}?{r1}?{y2}?{r2}?{y3}?{r3}?{y2}?{y1}{d21}?{y3}?{y2}{d32}?</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>name,base_name,y1,r1,y2,r2,y3,r3,d21,d32</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>????-????</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>summary_income_struct_intro</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>{name}????????</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>????-??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>summary_total_not_applicable</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>{name}????????????????</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>????-??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>summary_struct_pending</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>{name}???????????</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>????-?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>summary_yoy_up</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>??{value}%</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>????-?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>summary_yoy_down</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>??{value}%</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>????-?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>summary_yoy_stable</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>???????{value}%?</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>????-?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>summary_pp_up</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>??{value}????</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>????-?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>summary_pp_down</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>??{value}????</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>????-?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>summary_pp_stable</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>???????{value}?????</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>????-?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>summary_top_missing</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>??????????</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>????-Top??</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>summary_top_line1</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>{y3}????????????????{top_txt}????????{cum}%?</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>y3,top_txt,cum</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>????-Top??</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>summary_top_line2</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>{y1}-{y3}??{move_txt}????{top_delta_txt}?</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>y1,y3,move_txt,top_delta_txt</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>????-Top???</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>summary_top_move_default</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>????????</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>????-Top????</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>summary_top_delta_pending</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>??????????</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>????-Top?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>summary_see_income_page</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>????????????</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>????-????</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>summary_sum008_struct</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>{y3}?????????{s_rec_3}??????????{s_non_3}?{y1}-{y3}??????????{d_rec}??????????{d_non}?</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>y3,s_rec_3,s_non_3,y1,d_rec,d_non</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>????-SUM008??</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>summary_sum009_trend_pending</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>?????????????</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>????-SUM009????</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>summary_sum009_struct</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>{y3}?????????????????{trend_txt}?</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>y3,trend_txt</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>????-SUM009??</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>summary_sum010_struct</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>{y3}???????????????????{gp_s3}??????????{ot_s3}?{y1}-{y3}????????????{d_gp}??????????{d_ot}?</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>y3,gp_s3,ot_s3,y1,d_gp,d_ot</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>????-SUM010??</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>summary_sum011_struct</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>{y3}?{name}?????????{r3}?{y1}-{y3}???{d_31}?</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>y3,name,r3,y1,d_31</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>????-SUM011??</t>
         </is>
       </c>
     </row>
@@ -7506,7 +8033,6 @@
           <t>global</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>2</v>
       </c>

--- a/config/rulebook.xlsx
+++ b/config/rulebook.xlsx
@@ -1888,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:F245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1923,6 +1923,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1932,20 +1937,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+          <t>{name}，{y1}年{v1}{unit}，{y2}年{v2}{unit}，{y3}年{v3}{unit}；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32,unit</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>???????</t>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>万元</t>
         </is>
       </c>
     </row>
@@ -1957,20 +1963,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{name}，{y1}年{v1}万元，{y2}年{v2}万元，{y3}年{v3}万元；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
+          <t>{name}，{y1}年{v1}{unit}，{y2}年{v2}{unit}，{y3}年{v3}{unit}；{y2}年较{y1}年{p21}，{y3}年较{y2}年{p32}。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32,unit</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>???????</t>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>万元</t>
         </is>
       </c>
     </row>
@@ -1988,11 +1995,7 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>????????</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2002,22 +2005,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+          <t>y1,r2_1,y2,r2_2,y3,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>??/???????</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2027,22 +2026,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>??????</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2058,11 +2053,7 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>????????</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2072,22 +2063,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+          <t>y1,r2_1,y2,r2_2,y3,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>??/???????</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2097,22 +2084,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>??????</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3572,12 +3555,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3597,12 +3580,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3622,12 +3605,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3647,12 +3630,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3672,12 +3655,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3697,12 +3680,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3722,12 +3705,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3747,12 +3730,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3772,12 +3755,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3797,12 +3780,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3822,12 +3805,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3847,12 +3830,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3872,12 +3855,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3897,12 +3880,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3922,12 +3905,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3947,12 +3930,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3972,12 +3955,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3997,12 +3980,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -4022,12 +4005,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -4047,12 +4030,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4072,12 +4055,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4097,12 +4080,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -4122,12 +4105,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4147,12 +4130,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4172,12 +4155,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4197,12 +4180,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4222,12 +4205,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4247,12 +4230,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+          <t>y1,r2_1,y2,r2_2,y3,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4272,12 +4255,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -4297,12 +4280,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4322,12 +4305,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4347,12 +4330,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4372,12 +4355,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4397,12 +4380,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -4422,12 +4405,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -4447,12 +4430,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4472,12 +4455,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4497,12 +4480,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4522,12 +4505,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4547,12 +4530,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4572,12 +4555,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4597,12 +4580,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4622,12 +4605,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4647,12 +4630,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4672,12 +4655,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4697,12 +4680,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4722,12 +4705,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4747,12 +4730,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4772,12 +4755,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4797,12 +4780,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4822,12 +4805,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4847,12 +4830,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4872,12 +4855,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4897,12 +4880,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4922,12 +4905,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4947,12 +4930,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4972,12 +4955,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>占总资产比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>占总资产比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+          <t>y1,r2_1,y2,r2_2,y3,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -6167,12 +6150,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6192,12 +6175,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6217,12 +6200,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6242,12 +6225,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6267,12 +6250,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6292,12 +6275,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6317,12 +6300,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6342,12 +6325,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6367,12 +6350,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6392,12 +6375,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6417,12 +6400,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6442,12 +6425,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6467,12 +6450,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6492,12 +6475,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6517,12 +6500,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6542,12 +6525,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6567,12 +6550,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6592,12 +6575,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -6617,12 +6600,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -6642,12 +6625,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -6667,12 +6650,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -6692,12 +6675,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -6717,12 +6700,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -6742,12 +6725,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -6767,12 +6750,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -6792,12 +6775,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -6817,12 +6800,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -6842,12 +6825,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -6867,12 +6850,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -6892,12 +6875,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -6917,12 +6900,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -6942,12 +6925,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+          <t>y1,r2_1,y2,r2_2,y3,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -6967,12 +6950,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -6992,12 +6975,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7017,12 +7000,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7042,12 +7025,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7067,12 +7050,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7092,12 +7075,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7117,12 +7100,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7142,12 +7125,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7167,12 +7150,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7192,12 +7175,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7217,12 +7200,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7242,12 +7225,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>{base1_label}：{y1}年{r11}%，{y2}年{r12}%，{y3}年{r13}%；{y2}较{y1}{r121}，{y3}较{y2}{r132}。占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>{base1_label}：{y1}年{r1_1}%，{y2}年{r1_2}%，{y3}年{r1_3}%；{y2}较{y1}{r1_21}，{y3}较{y2}{r1_32}。占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>base1_label,y1,r11,y2,r12,y3,r13,r121,r132,rt1,rt2,rt3,rt21,rt32</t>
+          <t>base1_label,y1,r1_1,y2,r1_2,y3,r1_3,r1_21,r1_32,r2_1,r2_2,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7267,12 +7250,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>占负债总计比例：{y1}年{rt1}%，{y2}年{rt2}%，{y3}年{rt3}%；{y2}较{y1}{rt21}，{y3}较{y2}{rt32}。</t>
+          <t>占负债总计比例：{y1}年{r2_1}%，{y2}年{r2_2}%，{y3}年{r2_3}%；{y2}较{y1}{r2_21}，{y3}较{y2}{r2_32}。</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>y1,rt1,y2,rt2,y3,rt3,rt21,rt32</t>
+          <t>y1,r2_1,y2,r2_2,y3,r2_3,r2_21,r2_32</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7462,20 +7445,20 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>{name}?{y1}?{v1}???{y2}?{v2}???{y3}?{v3}???{y2}?{y1}{p21}?{y3}?{y2}{p32}?</t>
+          <t>{name}：{y1}年{v1}{unit}，{y2}年{v2}{unit}，{y3}年{v3}{unit}；{y2}较{y1}{p21}，{y3}较{y2}{p32}。</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>name,y1,v1,y2,v2,y3,v3,p21,p32</t>
+          <t>name,y1,v1,y2,v2,y3,v3,p21,p32,unit</t>
         </is>
       </c>
       <c r="D224" t="n">
         <v>1</v>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>????-???</t>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>万元</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7470,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>{name}?{base_name}???{y1}?{r1}?{y2}?{r2}?{y3}?{r3}?{y2}?{y1}{d21}?{y3}?{y2}{d32}?</t>
+          <t>{name}占{base_name}比例：{y1}年{r1}，{y2}年{r2}，{y3}年{r3}；{y2}较{y1}{d21}，{y3}较{y2}{d32}。</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7497,11 +7480,6 @@
       </c>
       <c r="D225" t="n">
         <v>1</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>????-????</t>
-        </is>
       </c>
     </row>
     <row r="226">
@@ -7512,7 +7490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>{name}????????</t>
+          <t>{name}：分项结构如下。</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7522,11 +7500,6 @@
       </c>
       <c r="D226" t="n">
         <v>1</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>????-??????</t>
-        </is>
       </c>
     </row>
     <row r="227">
@@ -7537,7 +7510,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>{name}????????????????</t>
+          <t>{name}：为汇总项，结构占比分析不适用。</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7547,11 +7520,6 @@
       </c>
       <c r="D227" t="n">
         <v>1</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>????-??????</t>
-        </is>
       </c>
     </row>
     <row r="228">
@@ -7562,7 +7530,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>{name}???????????</t>
+          <t>{name}：结构占比分析待补充。</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7572,11 +7540,6 @@
       </c>
       <c r="D228" t="n">
         <v>1</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>????-?????</t>
-        </is>
       </c>
     </row>
     <row r="229">
@@ -7587,7 +7550,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>??{value}%</t>
+          <t>增加{value}%</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7597,11 +7560,6 @@
       </c>
       <c r="D229" t="n">
         <v>1</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>????-?????</t>
-        </is>
       </c>
     </row>
     <row r="230">
@@ -7612,7 +7570,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>??{value}%</t>
+          <t>减少{value}%</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7622,11 +7580,6 @@
       </c>
       <c r="D230" t="n">
         <v>1</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>????-?????</t>
-        </is>
       </c>
     </row>
     <row r="231">
@@ -7637,7 +7590,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>???????{value}%?</t>
+          <t>基本稳定（变动{value}%）</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7647,11 +7600,6 @@
       </c>
       <c r="D231" t="n">
         <v>1</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>????-?????</t>
-        </is>
       </c>
     </row>
     <row r="232">
@@ -7662,7 +7610,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>??{value}????</t>
+          <t>上升{value}个百分点</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7672,11 +7620,6 @@
       </c>
       <c r="D232" t="n">
         <v>1</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>????-?????</t>
-        </is>
       </c>
     </row>
     <row r="233">
@@ -7687,7 +7630,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>??{value}????</t>
+          <t>下降{value}个百分点</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7697,11 +7640,6 @@
       </c>
       <c r="D233" t="n">
         <v>1</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>????-?????</t>
-        </is>
       </c>
     </row>
     <row r="234">
@@ -7712,7 +7650,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>???????{value}?????</t>
+          <t>基本稳定（变动{value}个百分点）</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7722,11 +7660,6 @@
       </c>
       <c r="D234" t="n">
         <v>1</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>????-?????</t>
-        </is>
       </c>
     </row>
     <row r="235">
@@ -7737,16 +7670,11 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>结构迁移分析待补充。</t>
         </is>
       </c>
       <c r="D235" t="n">
         <v>1</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>????-Top??</t>
-        </is>
       </c>
     </row>
     <row r="236">
@@ -7757,7 +7685,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>{y3}????????????????{top_txt}????????{cum}%?</t>
+          <t>{y3}年内部构成按占比从高到低分别为：{top_txt}，这几项占比合计{cum}%。</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7767,11 +7695,6 @@
       </c>
       <c r="D236" t="n">
         <v>1</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>????-Top??</t>
-        </is>
       </c>
     </row>
     <row r="237">
@@ -7782,7 +7705,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>{y1}-{y3}??{move_txt}????{top_delta_txt}?</t>
+          <t>{y1}-{y3}年，{move_txt}；同时，{top_delta_txt}。</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7792,11 +7715,6 @@
       </c>
       <c r="D237" t="n">
         <v>1</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>????-Top???</t>
-        </is>
       </c>
     </row>
     <row r="238">
@@ -7807,16 +7725,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>????????</t>
+          <t>内部结构整体稳定</t>
         </is>
       </c>
       <c r="D238" t="n">
         <v>1</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>????-Top????</t>
-        </is>
       </c>
     </row>
     <row r="239">
@@ -7827,16 +7740,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>主要构成项变化待补充</t>
         </is>
       </c>
       <c r="D239" t="n">
         <v>1</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>????-Top?????</t>
-        </is>
       </c>
     </row>
     <row r="240">
@@ -7847,17 +7755,11 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>????????????</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
+          <t>详见“收入分析”子页面。</t>
+        </is>
+      </c>
       <c r="D240" t="n">
         <v>1</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>????-????</t>
-        </is>
       </c>
     </row>
     <row r="241">
@@ -7868,7 +7770,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>{y3}?????????{s_rec_3}??????????{s_non_3}?{y1}-{y3}??????????{d_rec}??????????{d_non}?</t>
+          <t>{y3}年经常性净收益占比{s_rec_3}、非经常性净收益占比{s_non_3}；{y1}-{y3}年，经常性净收益占比{d_rec}；非经常性净收益占比{d_non}。</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7878,11 +7780,6 @@
       </c>
       <c r="D241" t="n">
         <v>1</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>????-SUM008??</t>
-        </is>
       </c>
     </row>
     <row r="242">
@@ -7893,17 +7790,11 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>?????????????</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
+          <t>各子业务毛利结构趋势待补充</t>
+        </is>
+      </c>
       <c r="D242" t="n">
         <v>1</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>????-SUM009????</t>
-        </is>
       </c>
     </row>
     <row r="243">
@@ -7914,7 +7805,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>{y3}?????????????????{trend_txt}?</t>
+          <t>{y3}年各子业务毛利影响占比及结构变化：{trend_txt}。</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7924,11 +7815,6 @@
       </c>
       <c r="D243" t="n">
         <v>1</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>????-SUM009??</t>
-        </is>
       </c>
     </row>
     <row r="244">
@@ -7939,7 +7825,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>{y3}???????????????????{gp_s3}??????????{ot_s3}?{y1}-{y3}????????????{d_gp}??????????{d_ot}?</t>
+          <t>{y3}年经常性净收益中，主营业务毛利收益占比{gp_s3}，其他经常性收益占比{ot_s3}；{y1}-{y3}年，主营业务毛利收益占比{d_gp}，其他经常性收益占比{d_ot}。</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7949,11 +7835,6 @@
       </c>
       <c r="D244" t="n">
         <v>1</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>????-SUM010??</t>
-        </is>
       </c>
     </row>
     <row r="245">
@@ -7964,7 +7845,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>{y3}?{name}?????????{r3}?{y1}-{y3}???{d_31}?</t>
+          <t>{y3}年{name}占经营净收益比例为{r3}；{y1}-{y3}年占比{d_31}。</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7974,11 +7855,6 @@
       </c>
       <c r="D245" t="n">
         <v>1</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>????-SUM011??</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/config/rulebook.xlsx
+++ b/config/rulebook.xlsx
@@ -12,6 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务比率规则" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis_text_templates" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis_thresholds" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary_analysis_items" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary_exclude_codes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis_code_redirects" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1948,7 +1951,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>万元</t>
@@ -1974,7 +1976,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>万元</t>
@@ -1995,7 +1996,6 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2016,7 +2016,6 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2037,7 +2036,6 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2053,7 +2051,6 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2074,7 +2071,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2095,7 +2091,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7927,4 +7922,571 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>source_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>code_candidates</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>name_keywords</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SUM001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>流动资产</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BS000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BS000,BS027</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SUM002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>非流动资产</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BS028</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BS028,BS056</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SUM003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>资产总计</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BS057</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BS057</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUM004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>流动负债</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BS058</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BS058,BS089</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUM005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>非流动负债</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BS090</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BS090,BS102</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUM006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>负债总计</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BS103</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BS103</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SUM007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>营业收入</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IS001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IS001</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>营业总收入,营业收入</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SUM008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>经营净收益</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>income_combo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.1+3.2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SUM009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>主营业务毛利收益</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>income_node</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUM010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>经常性净收益</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>income_node</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUM011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>非经常性净收益</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>income_node</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>summary_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>exclude_codes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SUM001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BS004,BS009,BS015</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SUM002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BS041,BS044</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SUM004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BS062,BS070</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUM005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BS094</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>group_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>src_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dst_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>asset_analysis</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BS028</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BS056</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>liability_analysis</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BS058</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BS089</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>liability_analysis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BS090</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BS102</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/config/rulebook.xlsx
+++ b/config/rulebook.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary_analysis_items" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary_exclude_codes" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis_code_redirects" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary_composition_policy" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -580,6 +581,150 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dedup_enabled</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>??????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dedup_share_near_pp</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>????&lt;=??(???)???????</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dedup_contains_enabled</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dedup_keep_existing_if_contains_ji</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>??????????????????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>top_max_items</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Top???????0??????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>top_delta_max_items</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>????????????????Top????0?????</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7996,7 +8141,6 @@
           <t>BS000,BS027</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>1</v>
       </c>
@@ -8027,7 +8171,6 @@
           <t>BS028,BS056</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>1</v>
       </c>
@@ -8058,7 +8201,6 @@
           <t>BS057</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>1</v>
       </c>
@@ -8089,7 +8231,6 @@
           <t>BS058,BS089</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>1</v>
       </c>
@@ -8120,7 +8261,6 @@
           <t>BS090,BS102</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>1</v>
       </c>
@@ -8151,7 +8291,6 @@
           <t>BS103</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>1</v>
       </c>
@@ -8212,8 +8351,6 @@
           <t>3.1+3.2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>1</v>
       </c>
@@ -8239,8 +8376,6 @@
           <t>2.1.1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>1</v>
       </c>
@@ -8266,8 +8401,6 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>1</v>
       </c>
@@ -8293,8 +8426,6 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>1</v>
       </c>
